--- a/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 23,0</t>
+          <t>17,53; 23,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,08; 51,23</t>
+          <t>43,71; 50,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,64; 42,06</t>
+          <t>34,71; 42,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,63; 29,96</t>
+          <t>22,84; 29,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,6; 28,63</t>
+          <t>23,52; 28,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 48,79</t>
+          <t>43,2; 49,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,5; 44,39</t>
+          <t>37,59; 44,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,04; 39,69</t>
+          <t>34,05; 39,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 25,57</t>
+          <t>21,9; 25,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,49; 48,78</t>
+          <t>44,4; 48,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,32; 42,44</t>
+          <t>37,47; 42,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,62; 35,08</t>
+          <t>30,7; 35,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,58; 24,27</t>
+          <t>19,73; 24,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,9; 57,0</t>
+          <t>52,12; 57,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,19; 44,04</t>
+          <t>39,03; 44,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,22; 25,21</t>
+          <t>20,28; 25,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,18; 28,21</t>
+          <t>23,44; 28,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,55; 62,92</t>
+          <t>57,6; 62,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,99; 51,95</t>
+          <t>46,94; 52,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,19; 53,02</t>
+          <t>22,05; 55,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 25,76</t>
+          <t>22,41; 25,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55,54; 59,34</t>
+          <t>55,52; 59,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,68; 47,32</t>
+          <t>43,81; 47,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,08; 42,91</t>
+          <t>22,16; 43,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,07; 29,42</t>
+          <t>20,36; 29,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,1; 56,91</t>
+          <t>45,43; 56,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,53; 53,72</t>
+          <t>42,14; 53,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 25,2</t>
+          <t>16,32; 25,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,8; 32,63</t>
+          <t>22,99; 31,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,7; 61,36</t>
+          <t>50,66; 61,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,24; 56,53</t>
+          <t>46,34; 56,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,95; 23,18</t>
+          <t>16,9; 23,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,82; 29,66</t>
+          <t>23,31; 29,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,17; 57,52</t>
+          <t>49,7; 57,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,83; 53,61</t>
+          <t>45,83; 53,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 22,83</t>
+          <t>17,39; 22,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,24; 23,52</t>
+          <t>20,23; 23,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,96; 53,82</t>
+          <t>49,69; 53,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,6; 43,64</t>
+          <t>39,44; 43,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 24,68</t>
+          <t>20,99; 24,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,72; 27,85</t>
+          <t>24,54; 27,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,48; 56,14</t>
+          <t>52,31; 55,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,95; 48,81</t>
+          <t>45,21; 48,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 48,86</t>
+          <t>25,58; 48,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,03; 25,45</t>
+          <t>23,06; 25,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,62; 54,51</t>
+          <t>51,73; 54,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,26; 45,85</t>
+          <t>43,08; 45,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,28; 40,51</t>
+          <t>24,13; 38,28</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>158750; 203785</t>
+          <t>155303; 205152</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383702; 446002</t>
+          <t>380475; 441948</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>225050; 273270</t>
+          <t>225489; 275082</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99061; 131134</t>
+          <t>99991; 131157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>284297; 344884</t>
+          <t>283365; 346171</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>544922; 617196</t>
+          <t>546455; 621909</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>348783; 412787</t>
+          <t>349635; 412112</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>231895; 270418</t>
+          <t>231944; 269213</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>456301; 534548</t>
+          <t>457973; 534578</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>950065; 1041640</t>
+          <t>948230; 1042781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>589604; 670382</t>
+          <t>591980; 671908</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>342680; 392514</t>
+          <t>343552; 393998</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>233963; 290111</t>
+          <t>235817; 293239</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>786447; 863761</t>
+          <t>789896; 864941</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>585048; 657477</t>
+          <t>582557; 659410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265586; 331064</t>
+          <t>266375; 331467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>299011; 363937</t>
+          <t>302366; 363813</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>867075; 948015</t>
+          <t>867858; 947548</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>756243; 836062</t>
+          <t>755464; 838302</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>387367; 925413</t>
+          <t>384849; 970836</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>554939; 640226</t>
+          <t>556897; 642110</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1678455; 1793305</t>
+          <t>1677797; 1788782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1355067; 1467874</t>
+          <t>1359151; 1473453</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>675499; 1312519</t>
+          <t>677871; 1331358</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76926; 112739</t>
+          <t>78030; 113610</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>161171; 203372</t>
+          <t>162359; 203100</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146664; 185228</t>
+          <t>145324; 185062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68242; 104655</t>
+          <t>67776; 104640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90122; 123549</t>
+          <t>87048; 121123</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>186990; 226297</t>
+          <t>186818; 228406</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>188761; 230788</t>
+          <t>189177; 229280</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76143; 104120</t>
+          <t>75919; 104376</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>173827; 225978</t>
+          <t>177582; 226264</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>364313; 417714</t>
+          <t>360883; 419854</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345121; 403678</t>
+          <t>345156; 401741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>149934; 197387</t>
+          <t>150364; 195928</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>498707; 579750</t>
+          <t>498664; 585848</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1370490; 1476420</t>
+          <t>1363132; 1473735</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>984898; 1085331</t>
+          <t>980867; 1088643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>453761; 534708</t>
+          <t>454729; 533372</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>710346; 800129</t>
+          <t>705160; 801015</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1648152; 1763189</t>
+          <t>1642877; 1757351</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1324914; 1438718</t>
+          <t>1332601; 1439290</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>737180; 1405245</t>
+          <t>735755; 1382477</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1229084; 1358587</t>
+          <t>1231143; 1358193</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3037134; 3207429</t>
+          <t>3043417; 3199530</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2351052; 2492132</t>
+          <t>2341347; 2495818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1224059; 2042570</t>
+          <t>1216908; 1930034</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,53; 23,15</t>
+          <t>17,97; 23,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,71; 50,77</t>
+          <t>43,84; 50,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,71; 42,34</t>
+          <t>34,78; 42,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,84; 29,96</t>
+          <t>22,71; 29,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,52; 28,73</t>
+          <t>23,81; 28,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,2; 49,16</t>
+          <t>43,28; 49,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,59; 44,31</t>
+          <t>37,16; 43,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,05; 39,52</t>
+          <t>34,8; 40,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,9; 25,57</t>
+          <t>21,88; 25,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,4; 48,83</t>
+          <t>44,67; 48,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,47; 42,53</t>
+          <t>37,17; 42,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,7; 35,21</t>
+          <t>30,87; 35,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 24,54</t>
+          <t>19,58; 24,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,12; 57,08</t>
+          <t>51,67; 56,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,03; 44,17</t>
+          <t>39,05; 44,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,28; 25,24</t>
+          <t>21,85; 26,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,44; 28,2</t>
+          <t>23,46; 28,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,6; 62,89</t>
+          <t>57,63; 63,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,94; 52,09</t>
+          <t>46,93; 51,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,05; 55,62</t>
+          <t>23,57; 27,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,41; 25,84</t>
+          <t>22,3; 25,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55,52; 59,19</t>
+          <t>55,42; 59,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,81; 47,5</t>
+          <t>43,88; 47,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 43,53</t>
+          <t>23,42; 26,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,36; 29,64</t>
+          <t>20,42; 29,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,43; 56,83</t>
+          <t>45,4; 57,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,14; 53,67</t>
+          <t>42,01; 53,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 25,19</t>
+          <t>17,03; 26,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,99; 31,99</t>
+          <t>23,12; 33,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,66; 61,93</t>
+          <t>50,61; 61,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,34; 56,16</t>
+          <t>45,8; 56,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 23,24</t>
+          <t>17,21; 23,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,31; 29,7</t>
+          <t>23,08; 29,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,7; 57,82</t>
+          <t>49,36; 57,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,83; 53,35</t>
+          <t>46,36; 53,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 22,67</t>
+          <t>18,36; 23,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,77</t>
+          <t>20,06; 23,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,69; 53,72</t>
+          <t>49,75; 53,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,44; 43,77</t>
+          <t>39,72; 43,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,99; 24,62</t>
+          <t>22,46; 26,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,54; 27,88</t>
+          <t>24,55; 27,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,31; 55,96</t>
+          <t>52,12; 55,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,21; 48,83</t>
+          <t>44,93; 48,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,58; 48,07</t>
+          <t>26,4; 29,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,06; 25,44</t>
+          <t>23,05; 25,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,73; 54,38</t>
+          <t>51,79; 54,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,08; 45,92</t>
+          <t>43,1; 45,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,13; 38,28</t>
+          <t>24,83; 27,28</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114413</t>
+          <t>125379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>251457</t>
+          <t>278715</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>365870</t>
+          <t>404094</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>155303; 205152</t>
+          <t>159224; 205943</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>380475; 441948</t>
+          <t>381636; 442565</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>225489; 275082</t>
+          <t>225941; 275404</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99991; 131157</t>
+          <t>108692; 142648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>283365; 346171</t>
+          <t>286872; 345821</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>546455; 621909</t>
+          <t>547511; 621142</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>349635; 412112</t>
+          <t>345605; 407267</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>231944; 269213</t>
+          <t>259326; 299309</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>457973; 534578</t>
+          <t>457524; 536849</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>948230; 1042781</t>
+          <t>953906; 1044809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>591980; 671908</t>
+          <t>587209; 665670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>343552; 393998</t>
+          <t>377783; 430432</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>296667</t>
+          <t>348450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>562527</t>
+          <t>414441</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>859194</t>
+          <t>762890</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>235817; 293239</t>
+          <t>233982; 290353</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>789896; 864941</t>
+          <t>783024; 862503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>582557; 659410</t>
+          <t>582973; 657238</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>266375; 331467</t>
+          <t>313315; 381554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>302366; 363813</t>
+          <t>302620; 362892</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>867858; 947548</t>
+          <t>868218; 949655</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>755464; 838302</t>
+          <t>755355; 835050</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>384849; 970836</t>
+          <t>382060; 449088</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>556897; 642110</t>
+          <t>554164; 639706</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1677797; 1788782</t>
+          <t>1674889; 1788257</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1359151; 1473453</t>
+          <t>1361332; 1475009</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>677871; 1331358</t>
+          <t>715600; 815303</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84388</t>
+          <t>96553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89634</t>
+          <t>104012</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>174021</t>
+          <t>200565</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78030; 113610</t>
+          <t>78247; 112003</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>162359; 203100</t>
+          <t>162254; 203862</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145324; 185062</t>
+          <t>144856; 184686</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67776; 104640</t>
+          <t>77794; 119362</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87048; 121123</t>
+          <t>87550; 125439</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>186818; 228406</t>
+          <t>186627; 227512</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>189177; 229280</t>
+          <t>186956; 229422</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75919; 104376</t>
+          <t>87361; 120187</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>177582; 226264</t>
+          <t>175834; 222291</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>360883; 419854</t>
+          <t>358456; 417978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345156; 401741</t>
+          <t>349136; 403827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>150364; 195928</t>
+          <t>177033; 225292</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>495468</t>
+          <t>570382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>903617</t>
+          <t>797167</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1399085</t>
+          <t>1367549</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>498664; 585848</t>
+          <t>494437; 581117</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1363132; 1473735</t>
+          <t>1364802; 1472924</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>980867; 1088643</t>
+          <t>987827; 1089182</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>454729; 533372</t>
+          <t>532286; 617585</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>705160; 801015</t>
+          <t>705373; 797847</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1642877; 1757351</t>
+          <t>1636717; 1753473</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1332601; 1439290</t>
+          <t>1324328; 1442155</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>735755; 1382477</t>
+          <t>758654; 840019</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1231143; 1358193</t>
+          <t>1230628; 1358434</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3043417; 3199530</t>
+          <t>3047402; 3200227</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2341347; 2495818</t>
+          <t>2342542; 2492814</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1216908; 1930034</t>
+          <t>1301943; 1430383</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
